--- a/service_bookings.xlsx
+++ b/service_bookings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -585,6 +585,33 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>Dynamic website</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>swethaharish2222@gmail.com</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>9047516035</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Static Websites</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>personalized porfolio</t>
         </is>
       </c>
     </row>

--- a/service_bookings.xlsx
+++ b/service_bookings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,6 +615,33 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>srfml</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>jsdj@fsdsfm.com</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7412588963321456987456</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Student Projects</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>lkmklor</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/service_bookings.xlsx
+++ b/service_bookings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -642,6 +642,60 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dhanusha</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>dhanusha.selvaraj05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>09344520475</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Dynamic Websites</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>dhanusha</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dhanusha.selvaraj05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>09344520475</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Dynamic Websites</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/service_bookings.xlsx
+++ b/service_bookings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -696,6 +696,60 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>dhanusha</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>dhanusha.selvaraj05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>09344520475</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Dynamic Websites</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>dhanusha</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>dhanusha.selvaraj05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>09344520475</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Dynamic Websites</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/service_bookings.xlsx
+++ b/service_bookings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -750,6 +750,381 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>dhanusha</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>dhanusha.selvaraj05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>09344520475</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Static Websites</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>dhanusha</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>dhanusha.selvaraj05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>09344520475</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Static Websites</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>dhanusha</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dhanusha.selvaraj05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>09344520475</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Dynamic Websites</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>dhanusha</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>dhanusha.selvaraj05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>9344520475</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Dynamic Websites</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>dhanusha</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>dhanusha.selvaraj05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>9344520475</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Dynamic Websites</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>dhanusha</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>dhanusha.selvaraj05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>9344520475</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Dynamic Websites</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>dhanusha</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>dhanusha.selvaraj05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>9344520475</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CRM projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>dhanusha</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>dhanusha.selvaraj05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>9344520475</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Static Websites</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>dhanusha</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>dhanusha.selvaraj05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>9344520475</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Static Websites</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>gopika</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>gopikas04082005@gmail.com</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>8248346453</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Static Websites</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>gopika</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>gopikas04082005@gmail.com</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>8248346453</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Dynamic Websites</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>gopika</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>gopikas04082005@gmail.com</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>8248346453</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Student Projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>gopika</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>gopikas04082005@gmail.com</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>8248346453</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Personal Portfolio</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>gopika</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>gopikas04082005@gmail.com</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>8248346453</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Resume preparation</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>gopika</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>gopikas04082005@gmail.com</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>8248346453</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Resume preparation</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>gopika</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>gopikas04082005@gmail.com</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>8248346453</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Resume preparation</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>gopika</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>gopikas04082005@gmail.com</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>8248346453</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CRM projects</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/service_bookings.xlsx
+++ b/service_bookings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1123,7 +1123,29 @@
           <t>CRM projects</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>dhanusha</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>dhanusha.selvaraj05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>9344520475</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Dynamic Websites</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
